--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_36_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_36_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2404</v>
+        <v>7.3999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2982</v>
+        <v>6.4241</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9422</v>
+        <v>0.9758</v>
       </c>
       <c r="G2" t="n">
         <v>4.1211</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2791</v>
+        <v>2.4386</v>
       </c>
       <c r="T2" t="n">
-        <v>4.3842</v>
+        <v>1.5101</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8949</v>
+        <v>0.9285</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7073</v>
+        <v>2.0706</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0931</v>
+        <v>1.6677</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8003</v>
+        <v>0.4029</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3586</v>
+        <v>-0.7546</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5688</v>
+        <v>-0.6826</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7617</v>
+        <v>0.1386</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.514</v>
+        <v>-0.4468</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2477</v>
+        <v>0.5854</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5969</v>
+        <v>-0.8932</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2759</v>
+        <v>0.3748</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3211</v>
+        <v>-1.2679</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.602</v>
+        <v>1.3818</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9006</v>
+        <v>0.4052</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7014</v>
+        <v>0.9766</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3987</v>
+        <v>2.0128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9285</v>
+        <v>2.8079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4701</v>
+        <v>-0.795</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7546</v>
+        <v>-0.422</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07199999999999999</v>
+        <v>2.5493</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6826</v>
+        <v>-2.9713</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1386</v>
+        <v>1.6077</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4468</v>
+        <v>2.5214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5854</v>
+        <v>-0.9137</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8932</v>
+        <v>-2.0297</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3748</v>
+        <v>0.0279</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2679</v>
+        <v>-2.0576</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7099</v>
+        <v>1.7543</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3339</v>
+        <v>0.5351</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0438</v>
+        <v>1.2193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2836</v>
+        <v>1.6083</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3558</v>
+        <v>3.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8863</v>
+        <v>1.4197</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7149</v>
+        <v>0.0563</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8286</v>
+        <v>1.3635</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.422</v>
+        <v>-1.3586</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5493</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9713</v>
+        <v>-0.5688</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6077</v>
+        <v>-0.7617</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5214</v>
+        <v>-0.514</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9137</v>
+        <v>-0.2477</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0297</v>
+        <v>-0.5969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0279</v>
+        <v>-0.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0576</v>
+        <v>-0.3211</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6278</v>
+        <v>2.3145</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5579</v>
+        <v>1.0499</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1857</v>
+        <v>1.2645</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.395</v>
+        <v>1.374</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1368</v>
+        <v>0.7669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.6071</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0732</v>
+        <v>1.9038</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5114</v>
+        <v>0.8498</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4383</v>
+        <v>1.054</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0872</v>
+        <v>1.7929</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0504</v>
+        <v>0.5783</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>1.2146</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.014</v>
+        <v>0.1109</v>
       </c>
       <c r="N6" t="n">
-        <v>0.461</v>
+        <v>0.2714</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4751</v>
+        <v>-0.1605</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0905</v>
+        <v>0.63</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.3657</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1336</v>
+        <v>0.2642</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3324</v>
+        <v>0.7488</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0278</v>
+        <v>0.217</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3046</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9038</v>
+        <v>0.0732</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8498</v>
+        <v>0.5114</v>
       </c>
       <c r="I7" t="n">
-        <v>1.054</v>
+        <v>-0.4383</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7929</v>
+        <v>0.0872</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5783</v>
+        <v>0.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2146</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1109</v>
+        <v>-0.014</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2714</v>
+        <v>0.461</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>-0.4751</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4116</v>
+        <v>0.2634</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.1298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0382</v>
+        <v>0.1336</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>V. TOLIOPOULOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9729</v>
+        <v>-0.0644</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1887</v>
+        <v>0.4534</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7843</v>
+        <v>-0.5178</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4283</v>
+        <v>-2.2591</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3517</v>
+        <v>0.3304</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.78</v>
+        <v>-2.5895</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8156</v>
+        <v>0.7282</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2268</v>
+        <v>0.4705</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5889</v>
+        <v>0.2576</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2439</v>
+        <v>-2.9873</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1249</v>
+        <v>-0.1401</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3688</v>
+        <v>-2.8472</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0602</v>
+        <v>1.035</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8962</v>
+        <v>0.1891</v>
       </c>
       <c r="U8" t="n">
-        <v>0.836</v>
+        <v>0.8459</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1076</v>
+        <v>-0.5857</v>
       </c>
       <c r="E9" t="n">
-        <v>0.774</v>
+        <v>1.1278</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8816</v>
+        <v>-1.7135</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5551</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4107</v>
+        <v>0.1111</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1867</v>
+        <v>0.3547</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3089</v>
+        <v>-0.9215</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7795</v>
+        <v>0.1652</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0884</v>
+        <v>-1.0867</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3355</v>
+        <v>-0.4283</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2232</v>
+        <v>1.3517</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5587</v>
+        <v>-1.78</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6653</v>
+        <v>1.8156</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5917</v>
+        <v>1.2268</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>0.5889</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0008</v>
+        <v>-2.2439</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3684</v>
+        <v>0.1249</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6323</v>
+        <v>-2.3688</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2586</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>1.274</v>
+        <v>-0.5423</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0154</v>
+        <v>0.5335</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.2525</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5022</v>
+        <v>-1.0475</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1499</v>
+        <v>0.2039</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3523</v>
+        <v>-1.2514</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2707</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2315</v>
+        <v>0.2232</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1419</v>
+        <v>0.2427</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. TOLIOPOULOS</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4529</v>
+        <v>-1.959</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2294</v>
+        <v>0.0285</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2235</v>
+        <v>-1.9875</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2591</v>
+        <v>-0.3355</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3304</v>
+        <v>0.2232</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5895</v>
+        <v>-0.5587</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7282</v>
+        <v>0.6653</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4705</v>
+        <v>0.5917</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2576</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9873</v>
+        <v>-1.0008</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1401</v>
+        <v>-0.3684</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.8472</v>
+        <v>-0.6323</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1598</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3535</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4936</v>
+        <v>0.523</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1401</v>
+        <v>0.0854</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0102</v>
+        <v>-3.7071</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1282</v>
+        <v>-0.8923</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.882</v>
+        <v>-2.8148</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3053</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3286</v>
+        <v>-0.0255</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6054</v>
+        <v>6.740599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5968</v>
+        <v>13.0264</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.9917</v>
+        <v>-6.285600000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-3.5911</v>
@@ -1546,16 +1546,16 @@
         <v>9.7423</v>
       </c>
       <c r="S14" t="n">
-        <v>7.590799999999998</v>
+        <v>10.726</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2608</v>
+        <v>3.6902</v>
       </c>
       <c r="U14" t="n">
-        <v>6.330000000000001</v>
+        <v>7.0356</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3943000000000001</v>
+        <v>-0.3942999999999997</v>
       </c>
       <c r="W14" t="n">
         <v>4.745299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6341</v>
+        <v>2.5333</v>
       </c>
       <c r="E15" t="n">
         <v>2.9668</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3327</v>
+        <v>-0.4335</v>
       </c>
       <c r="G15" t="n">
         <v>3.9361</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2324</v>
+        <v>-0.3332</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1999</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6002</v>
+        <v>1.7854</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4666</v>
+        <v>3.5845</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8664</v>
+        <v>-1.7992</v>
       </c>
       <c r="G16" t="n">
         <v>2.7355</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4963</v>
+        <v>-1.3111</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6238</v>
+        <v>-0.5566</v>
       </c>
       <c r="V16" t="n">
         <v>2.6805</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2533</v>
+        <v>1.2869</v>
       </c>
       <c r="E17" t="n">
         <v>1.1778</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0755</v>
+        <v>0.1091</v>
       </c>
       <c r="G17" t="n">
         <v>0.9989</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8566</v>
+        <v>0.9745</v>
       </c>
       <c r="E18" t="n">
-        <v>2.874</v>
+        <v>2.992</v>
       </c>
       <c r="F18" t="n">
         <v>-2.0174</v>
@@ -1858,10 +1858,10 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.861</v>
+        <v>-0.7431</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6642</v>
+        <v>-0.5463</v>
       </c>
       <c r="U18" t="n">
         <v>-0.1968</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5713</v>
+        <v>0.4659</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4415</v>
+        <v>0.1364</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8702</v>
+        <v>0.3295</v>
       </c>
       <c r="G19" t="n">
-        <v>2.026</v>
+        <v>-0.3478</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.025</v>
+        <v>0.5523</v>
       </c>
       <c r="I19" t="n">
-        <v>2.051</v>
+        <v>-0.9002</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4487</v>
+        <v>0.0351</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5546</v>
+        <v>1.1427</v>
       </c>
       <c r="L19" t="n">
-        <v>2.8942</v>
+        <v>-1.1077</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4227</v>
+        <v>-0.3829</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5796</v>
+        <v>-0.5904</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8431</v>
+        <v>0.2075</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4551</v>
+        <v>-0.9544</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0589</v>
+        <v>-0.7389</v>
       </c>
       <c r="U19" t="n">
-        <v>0.514</v>
+        <v>-0.2155</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5667</v>
+        <v>0.3696</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1364</v>
+        <v>1.4415</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4303</v>
+        <v>-1.0718</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3478</v>
+        <v>2.026</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5523</v>
+        <v>-0.025</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9002</v>
+        <v>2.051</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0351</v>
+        <v>3.4487</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1427</v>
+        <v>0.5546</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1077</v>
+        <v>2.8942</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3829</v>
+        <v>-1.4227</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5904</v>
+        <v>-0.5796</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2075</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8536</v>
+        <v>0.2535</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>-0.0589</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1147</v>
+        <v>0.3123</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.039</v>
+        <v>0.0955</v>
       </c>
       <c r="E21" t="n">
         <v>0.6245000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6635</v>
+        <v>-0.529</v>
       </c>
       <c r="G21" t="n">
         <v>0.1856</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0622</v>
+        <v>-0.9278</v>
       </c>
       <c r="T21" t="n">
         <v>-0.6721</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3901</v>
+        <v>-0.2557</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9528</v>
+        <v>-0.7175</v>
       </c>
       <c r="E22" t="n">
         <v>1.0151</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9679</v>
+        <v>-1.7327</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3417</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7735</v>
+        <v>-1.5382</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6642</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1092</v>
+        <v>-0.874</v>
       </c>
       <c r="V22" t="n">
         <v>1.4665</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4146</v>
+        <v>-1.095</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7188</v>
+        <v>-0.6008</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6958</v>
+        <v>-0.4942</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4798</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1668</v>
+        <v>-0.8472</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0206</v>
+        <v>-2.2222</v>
       </c>
       <c r="E24" t="n">
         <v>-2.6684</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6478</v>
+        <v>0.4462</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9526</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.622</v>
+        <v>-0.8237</v>
       </c>
       <c r="T24" t="n">
         <v>-0.6563</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0343</v>
+        <v>-0.1674</v>
       </c>
       <c r="V24" t="n">
         <v>0.3943</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9966</v>
+        <v>-4.0467</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8356</v>
+        <v>-2.7177</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.161</v>
+        <v>-1.3291</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2425</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8237</v>
+        <v>-0.8738</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1516</v>
+        <v>-0.3196</v>
       </c>
       <c r="V25" t="n">
         <v>0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1167</v>
+        <v>-5.4877</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.7119</v>
+        <v>-2.1837</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.4049</v>
+        <v>-3.304</v>
       </c>
       <c r="G26" t="n">
         <v>-2.6714</v>
@@ -2482,13 +2482,13 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5302</v>
+        <v>-0.9012</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0861</v>
+        <v>-0.5579</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4441</v>
+        <v>-0.3433</v>
       </c>
       <c r="V26" t="n">
         <v>-3.0748</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.058099999999999</v>
+        <v>-6.058000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>5.768000000000001</v>
+        <v>5.768000000000002</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.8262</v>
+        <v>-11.8261</v>
       </c>
       <c r="G27" t="n">
         <v>1.331999999999999</v>
@@ -2560,13 +2560,13 @@
         <v>9.2782</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.9442</v>
+        <v>-8.944199999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-6.189700000000001</v>
+        <v>-6.1898</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.7543</v>
+        <v>-2.7545</v>
       </c>
       <c r="V27" t="n">
         <v>0.3942999999999994</v>
